--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D3">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>426</v>
